--- a/DataSource/Results.xlsx
+++ b/DataSource/Results.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="47">
   <si>
     <t>TestCase</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="25.36328125"/>
@@ -2078,6 +2078,266 @@
         <v>9</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E62" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G62" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H62" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F63" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="E64" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F64" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G64" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="H64" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E65" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F65" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="G65" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="H65" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E66" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F66" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="H66" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E67" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F67" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G67" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H67" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E68" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F68" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G68" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H68" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D69" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E69" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F69" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G69" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H69" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D70" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G70" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H70" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="D71" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F71" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G71" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H71" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
